--- a/data/trans_orig/IP29A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP29A_2023-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,65</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,84</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,21</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>9.651591639436731</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>8.835334759535158</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.205826857341277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7,16; 12,99</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,6; 12,6</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7,04; 11,86</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>7.15833505961182</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>5.60360031240974</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>7.044670737357575</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.9921176878286</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.60030179842195</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.85897218247042</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>8,39</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,36</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,59; 9,5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,54; 9,39</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7,8; 9,11</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>8.389340389078335</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>8.358560093984746</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>8.375019000204102</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8,89</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,26</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>7.590201776612094</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7.543708842115935</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>7.799357803185814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7,58; 10,58</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,18; 11,35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8,24; 10,41</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.500935812316829</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.389893048007757</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.109073385642152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,47 +661,107 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8,61</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,77</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,68</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>8.888177599618919</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.705680054492195</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.263894264916068</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7,83; 9,48</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,97; 9,64</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,16; 9,27</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>7.576451657401053</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>8.182990949333904</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>8.241533064957094</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.57716473400013</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.35401522522405</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.41332053898667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>8.611731252568058</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8.765682518218622</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8.684056477964486</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7.833070151589217</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>7.969775667232789</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8.155318453215974</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.483729182055642</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9.642100439127596</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.270677110871977</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -744,11 +769,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
